--- a/app/database/MRA11/mroy_MRA1_03_gear.xlsx
+++ b/app/database/MRA11/mroy_MRA1_03_gear.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
   <si>
     <t xml:space="preserve">code</t>
   </si>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">            material_pump</t>
+    <t xml:space="preserve">material_pump</t>
   </si>
   <si>
     <t xml:space="preserve">spm_1725rpm</t>
@@ -79,13 +79,10 @@
     <t xml:space="preserve">8:1 Gear Ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">    NA</t>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">        Only available on pumps with motor RPM 1425 or less</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        NA</t>
   </si>
 </sst>
 </file>
@@ -393,14 +390,14 @@
   <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="51.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -448,7 +445,8 @@
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="G2" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -474,7 +472,8 @@
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="b">
+      <c r="G3" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -500,7 +499,8 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="b">
+      <c r="G4" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -526,7 +526,8 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="b">
+      <c r="G5" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -552,7 +553,8 @@
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="b">
+      <c r="G6" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -578,7 +580,8 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="b">
+      <c r="G7" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -604,7 +607,8 @@
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="b">
+      <c r="G8" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -630,7 +634,8 @@
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="b">
+      <c r="G9" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -656,7 +661,8 @@
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="b">
+      <c r="G10" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -682,7 +688,8 @@
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="b">
+      <c r="G11" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -700,7 +707,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>178</v>
@@ -708,7 +715,8 @@
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="b">
+      <c r="G12" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
